--- a/Data/SK Expense Sheet.xlsx
+++ b/Data/SK Expense Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d772b42a7a1256b2/Desktop/Business/TSK Constructions/Projects/Building Construction/SK Residence - Sundarapuram/Accounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{14C610B6-5BF1-4C1A-B1BB-21F4E218EE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3E34A8E-7A71-41EA-A1A6-199E0CDB990D}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{75A8DF96-7F00-4506-A551-51A2B008097E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFBD7EC2-6BB1-47DA-BE17-6E4E26BD3D55}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="356">
   <si>
     <t>DATE</t>
   </si>
@@ -1053,6 +1053,66 @@
   </si>
   <si>
     <t>Elevation Adv new design</t>
+  </si>
+  <si>
+    <t>Tiles transport amt</t>
+  </si>
+  <si>
+    <t>OTHERS</t>
+  </si>
+  <si>
+    <t>Tiles Unloading Labour</t>
+  </si>
+  <si>
+    <t>Tiles remaining purchase</t>
+  </si>
+  <si>
+    <t>Ramdev Hardwares</t>
+  </si>
+  <si>
+    <t>Selvam Plumbing</t>
+  </si>
+  <si>
+    <t>Carpenter Adv Craving</t>
+  </si>
+  <si>
+    <t>SCAFFOLDING</t>
+  </si>
+  <si>
+    <t>Elevation Charges Pending</t>
+  </si>
+  <si>
+    <t>Lab Payment</t>
+  </si>
+  <si>
+    <t>Toilet Waterproofing Probhu</t>
+  </si>
+  <si>
+    <t>AMT sheet part amount</t>
+  </si>
+  <si>
+    <t>Maosn Lab</t>
+  </si>
+  <si>
+    <t>Tiles Paste Transport</t>
+  </si>
+  <si>
+    <t>TILES LABOUR</t>
+  </si>
+  <si>
+    <t>Tiles Advance</t>
+  </si>
+  <si>
+    <t>Plumbing Work</t>
+  </si>
+  <si>
+    <t>Terrace StepsGrill Adv</t>
+  </si>
+  <si>
+    <t>Tiles Paste 20 Bags</t>
+  </si>
+  <si>
+    <t>Chakra Closed</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1194,14 +1254,38 @@
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
@@ -1312,16 +1396,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TAMIL" refreshedDate="46142.636025" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="374" xr:uid="{ECDDBE9B-8132-48D6-AEC8-4A5EB49DBA77}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TAMIL" refreshedDate="46157.6627912037" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="394" xr:uid="{ECDDBE9B-8132-48D6-AEC8-4A5EB49DBA77}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D1007" sheet="Expenses"/>
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="DATE" numFmtId="164">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-01-14T00:00:00" maxDate="2026-05-01T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-01-14T00:00:00" maxDate="2026-05-14T00:00:00"/>
     </cacheField>
     <cacheField name="TYPE OF EXPENSE" numFmtId="0">
-      <sharedItems containsBlank="1" count="27">
+      <sharedItems containsBlank="1" count="29">
         <s v="PETTY CASH"/>
         <s v="LABOUR TRANSPORT"/>
         <s v="MASON MATERIALS"/>
@@ -1345,6 +1429,8 @@
         <s v="JOINERIES"/>
         <s v="CARPENTER LABOUR"/>
         <s v="PILE-COMPOUND"/>
+        <s v="PAINTING LABOUR"/>
+        <s v="OTHERS"/>
         <m/>
         <s v="RENTAL TRANSPORT" u="1"/>
         <s v="PETROL-GENSET" u="1"/>
@@ -1367,7 +1453,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="374">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="394">
   <r>
     <d v="2025-09-11T00:00:00"/>
     <x v="0"/>
@@ -3607,8 +3693,128 @@
     <s v="Elevation Design Pending Amount"/>
   </r>
   <r>
+    <d v="2026-05-02T00:00:00"/>
+    <x v="10"/>
+    <n v="21725"/>
+    <s v="Mason Lab Payment"/>
+  </r>
+  <r>
+    <d v="2026-05-02T00:00:00"/>
+    <x v="3"/>
+    <n v="24500"/>
+    <s v="Flyash Brick"/>
+  </r>
+  <r>
+    <d v="2026-05-02T00:00:00"/>
+    <x v="23"/>
+    <n v="10000"/>
+    <s v="Painting Adv"/>
+  </r>
+  <r>
+    <d v="2026-05-07T00:00:00"/>
+    <x v="20"/>
+    <n v="50000"/>
+    <s v="UPVC Advance"/>
+  </r>
+  <r>
+    <d v="2026-05-07T00:00:00"/>
+    <x v="4"/>
+    <n v="909"/>
+    <s v="Lab Tea"/>
+  </r>
+  <r>
+    <d v="2026-05-08T00:00:00"/>
+    <x v="3"/>
+    <n v="50000"/>
+    <s v="Tiles amount"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="10"/>
+    <n v="10700"/>
+    <s v="Rajkumar Mason Payment"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="17"/>
+    <n v="5000"/>
+    <s v="Selvam Plumbing and Electrical Work"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="23"/>
+    <n v="10000"/>
+    <s v="Painter Adv"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="21"/>
+    <n v="5000"/>
+    <s v="Carpenter Lab"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="3"/>
+    <n v="178000"/>
+    <s v="Tiles amount"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="20"/>
+    <n v="20000"/>
+    <s v="UPVC Advance"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="3"/>
+    <n v="50000"/>
+    <s v="Ramdev Payment"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="3"/>
+    <n v="25000"/>
+    <s v="Palani muugan payment "/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="19"/>
+    <n v="1000"/>
+    <s v="Elevation Adv new design"/>
+  </r>
+  <r>
+    <d v="2026-05-11T00:00:00"/>
+    <x v="15"/>
+    <n v="700"/>
+    <s v="Drinking water Nithish"/>
+  </r>
+  <r>
+    <d v="2026-05-12T00:00:00"/>
+    <x v="7"/>
+    <n v="3200"/>
+    <s v="Tiles transport amt"/>
+  </r>
+  <r>
+    <d v="2026-05-12T00:00:00"/>
+    <x v="24"/>
+    <n v="2800"/>
+    <s v="Tiles Unloading Labour"/>
+  </r>
+  <r>
+    <d v="2026-05-12T00:00:00"/>
+    <x v="3"/>
+    <n v="2845"/>
+    <s v="Tiles remaining purchase"/>
+  </r>
+  <r>
+    <d v="2026-05-13T00:00:00"/>
+    <x v="23"/>
+    <n v="3000"/>
+    <s v="Painter Adv"/>
+  </r>
+  <r>
     <m/>
-    <x v="23"/>
+    <x v="25"/>
     <m/>
     <m/>
   </r>
@@ -3616,29 +3822,29 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC8C9A3-14B4-46FA-8D51-AAF7A0B6E9CA}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
-  <location ref="A3:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC8C9A3-14B4-46FA-8D51-AAF7A0B6E9CA}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+  <location ref="A3:B29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="28">
+      <items count="30">
         <item x="3"/>
         <item x="6"/>
         <item x="5"/>
         <item x="2"/>
         <item x="7"/>
-        <item m="1" x="25"/>
+        <item m="1" x="27"/>
         <item x="0"/>
-        <item h="1" x="23"/>
+        <item h="1" x="25"/>
         <item x="10"/>
         <item x="9"/>
         <item x="4"/>
-        <item m="1" x="26"/>
+        <item m="1" x="28"/>
         <item x="13"/>
         <item x="11"/>
         <item x="1"/>
         <item x="8"/>
-        <item m="1" x="24"/>
+        <item m="1" x="26"/>
         <item x="12"/>
         <item x="14"/>
         <item x="15"/>
@@ -3649,6 +3855,8 @@
         <item x="20"/>
         <item x="21"/>
         <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3658,7 +3866,7 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="24">
+  <rowItems count="26">
     <i>
       <x/>
     </i>
@@ -3728,6 +3936,12 @@
     <i>
       <x v="26"/>
     </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -3738,29 +3952,56 @@
   <dataFields count="1">
     <dataField name="Total_Amount" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
-  <formats count="5">
-    <format dxfId="5">
+  <formats count="8">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="7">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="17"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
     <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="18"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -4051,7 +4292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.08984375" style="5" bestFit="1" customWidth="1"/>
@@ -4085,7 +4326,7 @@
       </c>
       <c r="J1" s="8">
         <f>SUM(B2:B201)</f>
-        <v>4550000</v>
+        <v>4650000</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -4131,7 +4372,7 @@
       </c>
       <c r="J3" s="8">
         <f>SUMIF(C2:C101,"SK",B2:B101)</f>
-        <v>4250000</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -4752,6 +4993,23 @@
         <v>19</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B37" s="7">
+        <v>100000</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>320</v>
       </c>
     </row>
@@ -4763,7 +5021,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E716AC5E-A74E-4151-8738-1C2F14C945B6}">
-  <dimension ref="A1:L389"/>
+  <dimension ref="A1:L417"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" style="5" bestFit="1" customWidth="1"/>
@@ -4798,7 +5056,7 @@
       </c>
       <c r="J1" s="7">
         <f>'Payment Received'!J1</f>
-        <v>4550000</v>
+        <v>4650000</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -4819,7 +5077,7 @@
       </c>
       <c r="J2" s="7">
         <f>SUM(C2:C508)</f>
-        <v>4391660</v>
+        <v>4734835</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -4840,7 +5098,7 @@
       </c>
       <c r="J3" s="7">
         <f>J1-J2</f>
-        <v>158340</v>
+        <v>-84835</v>
       </c>
       <c r="K3" t="s">
         <v>228</v>
@@ -4877,7 +5135,7 @@
       </c>
       <c r="J5" s="8">
         <f>J3-150000</f>
-        <v>8340</v>
+        <v>-234835</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -10273,14 +10531,406 @@
       <c r="A389" s="4">
         <v>46151</v>
       </c>
-      <c r="B389" s="29" t="s">
+      <c r="B389" s="1" t="s">
         <v>219</v>
       </c>
       <c r="C389" s="7">
         <v>1000</v>
       </c>
-      <c r="D389" s="29" t="s">
+      <c r="D389" s="1" t="s">
         <v>335</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A390" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C390" s="7">
+        <v>700</v>
+      </c>
+      <c r="D390" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A391" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C391" s="7">
+        <v>3200</v>
+      </c>
+      <c r="D391" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A392" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C392" s="7">
+        <v>2800</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A393" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C393" s="7">
+        <v>2845</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A394" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C394" s="7">
+        <v>3000</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A395" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C395" s="7">
+        <v>2675</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A396" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C396" s="7">
+        <v>30000</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A397" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C397" s="7">
+        <v>12000</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A398" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C398" s="7">
+        <v>5000</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A399" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C399" s="7">
+        <v>5000</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A400" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C400" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A401" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C401" s="7">
+        <v>50000</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A402" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C402" s="7">
+        <v>3000</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A403" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C403" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A404" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C404" s="7">
+        <v>59725</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A405" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C405" s="7">
+        <v>7500</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A406" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C406" s="7">
+        <v>2400</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A407" s="4">
+        <v>46169</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C407" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A408" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C408" s="7">
+        <v>24100</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A409" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C409" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A410" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C410" s="7">
+        <v>3500</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A411" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C411" s="7">
+        <v>630</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A412" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C412" s="7">
+        <v>31600</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A413" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C413" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A414" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C414" s="7">
+        <v>6000</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A415" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C415" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A416" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C416" s="7">
+        <v>11500</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A417" s="5">
+        <v>46179</v>
+      </c>
+      <c r="B417" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C417" s="8">
+        <v>30000</v>
+      </c>
+      <c r="D417" s="30" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -10291,7 +10941,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B21A9EA4-211D-4619-B47C-CA890DA4CB44}">
           <x14:formula1>
-            <xm:f>DataSource!$A$1:$A$31</xm:f>
+            <xm:f>DataSource!$A$1:$A$32</xm:f>
           </x14:formula1>
           <xm:sqref>B1:B1048576</xm:sqref>
         </x14:dataValidation>
@@ -10303,7 +10953,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCAE1F4E-AA4E-4ECE-A323-49517B1EF568}">
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
@@ -10361,92 +11011,107 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>209</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" s="28" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="28" t="s">
         <v>317</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="28" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="28" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -10456,14 +11121,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAED5D36-3AAD-4012-B629-BC62E5C1A2B7}">
-  <dimension ref="A3:B27"/>
+  <dimension ref="A3:E29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>18</v>
       </c>
@@ -10471,15 +11138,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="19">
-        <v>1570900</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1901245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>25</v>
       </c>
@@ -10487,7 +11154,7 @@
         <v>13820</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>36</v>
       </c>
@@ -10495,7 +11162,7 @@
         <v>20700</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>24</v>
       </c>
@@ -10503,15 +11170,15 @@
         <v>11710</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="19">
-        <v>18930</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>22130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>5</v>
       </c>
@@ -10519,15 +11186,15 @@
         <v>24405</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="19">
-        <v>792675</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>825100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>29</v>
       </c>
@@ -10535,15 +11202,15 @@
         <v>288425</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="19">
-        <v>22871</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>23780</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>28</v>
       </c>
@@ -10551,7 +11218,7 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>37</v>
       </c>
@@ -10559,7 +11226,7 @@
         <v>51410</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>39</v>
       </c>
@@ -10567,39 +11234,51 @@
         <v>10730</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="29" t="s">
         <v>52</v>
       </c>
       <c r="B16" s="19">
         <v>19500</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="15" t="s">
+      <c r="D16" s="20">
+        <f>SUM(B16:B18)</f>
+        <v>687250</v>
+      </c>
+      <c r="E16" s="20">
+        <f>D16+150000+200000</f>
+        <v>1037250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="29" t="s">
         <v>84</v>
       </c>
       <c r="B17" s="19">
         <v>39000</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="15" t="s">
+      <c r="E17" s="20">
+        <f>E16/2369</f>
+        <v>437.8429717180245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="29" t="s">
         <v>110</v>
       </c>
       <c r="B18" s="19">
         <v>628750</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>125</v>
       </c>
       <c r="B19" s="19">
-        <v>9100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>41</v>
       </c>
@@ -10607,15 +11286,15 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
         <v>30</v>
       </c>
       <c r="B21" s="19">
-        <v>27500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
         <v>209</v>
       </c>
@@ -10623,31 +11302,31 @@
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
         <v>219</v>
       </c>
       <c r="B23" s="19">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
         <v>253</v>
       </c>
       <c r="B24" s="19">
-        <v>138000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+        <v>208000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
         <v>275</v>
       </c>
       <c r="B25" s="19">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
         <v>317</v>
       </c>
@@ -10655,12 +11334,28 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="10" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="19">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="B28" s="19">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="20">
-        <v>3929826</v>
+      <c r="B29" s="20">
+        <v>4404205</v>
       </c>
     </row>
   </sheetData>
